--- a/ru/downloads/data-excel/3.3.4.xlsx
+++ b/ru/downloads/data-excel/3.3.4.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A40FC17-F594-4037-ADF5-62993C547310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15450" yWindow="750" windowWidth="13050" windowHeight="12990"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -145,7 +146,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -280,120 +281,114 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 6" xfId="2"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -409,9 +404,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -449,9 +444,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -486,7 +481,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -521,7 +516,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -694,43 +689,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.5703125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="35.140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="33.140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="1" width="35.5703125" customWidth="1"/>
+    <col min="2" max="2" width="35.140625" customWidth="1"/>
+    <col min="3" max="3" width="33.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="7" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -742,1927 +725,2021 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="U2" s="35"/>
+    </row>
+    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="6">
         <v>2007</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="6">
         <v>2008</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="6">
         <v>2009</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="6">
         <v>2010</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="6">
         <v>2011</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="6">
         <v>2012</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="6">
         <v>2013</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="6">
         <v>2014</v>
       </c>
-      <c r="L3" s="9">
+      <c r="L3" s="6">
         <v>2015</v>
       </c>
-      <c r="M3" s="9">
+      <c r="M3" s="6">
         <v>2016</v>
       </c>
-      <c r="N3" s="9">
+      <c r="N3" s="6">
         <v>2017</v>
       </c>
-      <c r="O3" s="9">
+      <c r="O3" s="6">
         <v>2018</v>
       </c>
-      <c r="P3" s="9">
+      <c r="P3" s="6">
         <v>2019</v>
       </c>
-      <c r="Q3" s="9">
+      <c r="Q3" s="6">
         <v>2020</v>
       </c>
-      <c r="R3" s="9">
+      <c r="R3" s="6">
         <v>2021</v>
       </c>
-      <c r="S3" s="9">
+      <c r="S3" s="6">
         <v>2022</v>
       </c>
-      <c r="T3" s="9">
+      <c r="T3" s="6">
         <v>2023</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" s="28" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+      <c r="U3" s="36">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" s="25" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="23">
         <v>12.090991831462583</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="23">
         <v>10.585235683186715</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="23">
         <v>10.866986781471583</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="23">
         <v>9.1593917723331302</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="23">
         <v>9.9551131383194971</v>
       </c>
-      <c r="I4" s="26">
+      <c r="I4" s="23">
         <v>10.075771585646466</v>
       </c>
-      <c r="J4" s="26">
+      <c r="J4" s="23">
         <v>8</v>
       </c>
-      <c r="K4" s="26">
+      <c r="K4" s="23">
         <v>7.5</v>
       </c>
-      <c r="L4" s="26">
+      <c r="L4" s="23">
         <v>5.9</v>
       </c>
-      <c r="M4" s="26">
+      <c r="M4" s="23">
         <v>6</v>
       </c>
-      <c r="N4" s="27">
+      <c r="N4" s="24">
         <v>5.3</v>
       </c>
-      <c r="O4" s="23">
+      <c r="O4" s="20">
         <v>5.1398717246167429</v>
       </c>
-      <c r="P4" s="37">
+      <c r="P4" s="32">
         <v>3.918522608558952</v>
       </c>
-      <c r="Q4" s="37">
+      <c r="Q4" s="32">
         <v>1.9148453093736542</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="32">
         <v>1.7931687443515183</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="32">
         <v>1.9210869108320343</v>
       </c>
-      <c r="T4" s="37">
+      <c r="T4" s="32">
         <v>2.3381104968484805</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="U4" s="37">
+        <v>1.3431427990652833</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="7">
         <v>10.263859863101086</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="7">
         <v>8.0885915981053405</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="7">
         <v>7.2250704811126756</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="7">
         <v>6.5972409758261863</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="7">
         <v>7.700462744086761</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="7">
         <v>7.0843445853402702</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="7">
         <v>6.4</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="7">
         <v>5.5</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="7">
         <v>4.2</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="7">
         <v>4.5</v>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="8">
         <v>4.3</v>
       </c>
-      <c r="O5" s="22">
+      <c r="O5" s="19">
         <v>3.5452203840759999</v>
       </c>
-      <c r="P5" s="38">
+      <c r="P5" s="33">
         <v>2.5208314439906609</v>
       </c>
-      <c r="Q5" s="38">
+      <c r="Q5" s="33">
         <v>1.7453236044300597</v>
       </c>
-      <c r="R5" s="38">
+      <c r="R5" s="33">
         <v>1.0977143806517458</v>
       </c>
-      <c r="S5" s="38">
+      <c r="S5" s="33">
         <v>1.020872301352429</v>
       </c>
-      <c r="T5" s="38">
+      <c r="T5" s="33">
         <v>2.0344672190198714</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="U5" s="38">
+        <v>1.0414165896566505</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="7">
         <v>13.967856230356499</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="7">
         <v>13.149995711957921</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="7">
         <v>14.604804528995055</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="7">
         <v>11.787756425535775</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="7">
         <v>12.267171652990362</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="7">
         <v>13.13951822007177</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="7">
         <v>9.5</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="7">
         <v>9.5</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="7">
         <v>7.5</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="7">
         <v>7.5</v>
       </c>
-      <c r="N6" s="11">
+      <c r="N6" s="8">
         <v>6.2</v>
       </c>
-      <c r="O6" s="22">
+      <c r="O6" s="19">
         <v>6.7607969448851533</v>
       </c>
-      <c r="P6" s="38">
+      <c r="P6" s="33">
         <v>5.3377117136239622</v>
       </c>
-      <c r="Q6" s="38">
+      <c r="Q6" s="33">
         <v>2.0818900906859255</v>
       </c>
-      <c r="R6" s="38">
+      <c r="R6" s="33">
         <v>2.4989281705678046</v>
       </c>
-      <c r="S6" s="38">
+      <c r="S6" s="33">
         <v>2.8415499553180767</v>
       </c>
-      <c r="T6" s="38">
+      <c r="T6" s="33">
         <v>2.6483752218014245</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+      <c r="U6" s="38">
+        <v>1.6512771369205415</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="7">
         <v>20.180532671095303</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="7">
         <v>20.012808197246237</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="7">
         <v>11.615831914265868</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="7">
         <v>4.5719301774823293</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="7">
         <v>11.68604977807742</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="7">
         <v>8.5927688545178142</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="7">
         <v>7.1</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="7">
         <v>5.7</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="7">
         <v>4.9000000000000004</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M7" s="7">
         <v>8.6</v>
       </c>
-      <c r="N7" s="11">
+      <c r="N7" s="8">
         <v>2.6</v>
       </c>
-      <c r="O7" s="22">
+      <c r="O7" s="19">
         <v>3.0807206575798243</v>
       </c>
-      <c r="P7" s="38">
+      <c r="P7" s="33">
         <v>4.8941637097760919</v>
       </c>
-      <c r="Q7" s="38">
+      <c r="Q7" s="33">
         <v>1.658050942694075</v>
       </c>
-      <c r="R7" s="38">
+      <c r="R7" s="33">
         <v>2.3489023398681002</v>
       </c>
-      <c r="S7" s="41">
+      <c r="S7" s="32">
         <v>1.5924017665043597</v>
       </c>
-      <c r="T7" s="41">
+      <c r="T7" s="32">
         <v>3.9852372948902328</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="U7" s="37">
+        <v>1.0186117340676393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="7">
         <v>18.345434883361655</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="7">
         <v>17.247244034130379</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="7">
         <v>9.4572485081190489</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="7">
         <v>3.2533928239449708</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="7">
         <v>8.2152017744835835</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="7">
         <v>6.2649631933412397</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="7">
         <v>7</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="7">
         <v>5.0999999999999996</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="7">
         <v>4.2</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="7">
         <v>9</v>
       </c>
-      <c r="N8" s="11">
+      <c r="N8" s="8">
         <v>2.8</v>
       </c>
-      <c r="O8" s="22">
+      <c r="O8" s="19">
         <v>2.7464012335264969</v>
       </c>
-      <c r="P8" s="38">
+      <c r="P8" s="33">
         <v>2.3023349513631741</v>
       </c>
-      <c r="Q8" s="38">
+      <c r="Q8" s="33">
         <v>1.4467487937731931</v>
       </c>
-      <c r="R8" s="38">
+      <c r="R8" s="33">
         <v>1.8410239038543676</v>
       </c>
-      <c r="S8" s="38">
+      <c r="S8" s="33">
         <v>2.5011433798307796</v>
       </c>
-      <c r="T8" s="38">
+      <c r="T8" s="33">
         <v>4.5532396299967433</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="U8" s="38">
+        <v>1.030364852194162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="7">
         <v>21.956255664246807</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="7">
         <v>22.685290209676896</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="7">
         <v>13.70056948700501</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="7">
         <v>5.8481636766055454</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="7">
         <v>15.052973183571009</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="7">
         <v>10.850458974414618</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="7">
         <v>7.2</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="7">
         <v>6.2</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="7">
         <v>5.7</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="7">
         <v>8.3000000000000007</v>
       </c>
-      <c r="N9" s="11">
+      <c r="N9" s="8">
         <v>2.2999999999999998</v>
       </c>
-      <c r="O9" s="22">
+      <c r="O9" s="19">
         <v>3.4029038112522687</v>
       </c>
-      <c r="P9" s="38">
+      <c r="P9" s="33">
         <v>7.3898906296186819</v>
       </c>
-      <c r="Q9" s="38">
+      <c r="Q9" s="33">
         <v>1.8774124750304142</v>
       </c>
-      <c r="R9" s="38">
+      <c r="R9" s="33">
         <v>2.8382683724659588</v>
       </c>
-      <c r="S9" s="38">
+      <c r="S9" s="33">
         <v>0.70098698968147144</v>
       </c>
-      <c r="T9" s="38">
+      <c r="T9" s="33">
         <v>3.4291318466903733</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+      <c r="U9" s="38">
+        <v>1.0071237217921429</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="7">
         <v>5.8703027456822907</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="7">
         <v>6.4034002055091248</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="7">
         <v>6.3057231334320569</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="7">
         <v>5.9229741486452898</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="7">
         <v>4.7826981113125155</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="7">
         <v>8.9163366057852951</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="7">
         <v>7.2</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="7">
         <v>5.8</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="7">
         <v>4.4000000000000004</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10" s="7">
         <v>2.6</v>
       </c>
-      <c r="N10" s="11">
+      <c r="N10" s="8">
         <v>3.3</v>
       </c>
-      <c r="O10" s="22">
+      <c r="O10" s="19">
         <v>2.6611093832380046</v>
       </c>
-      <c r="P10" s="38">
+      <c r="P10" s="33">
         <v>3.1795413633873366</v>
       </c>
-      <c r="Q10" s="38">
+      <c r="Q10" s="33">
         <v>0.96024351775610284</v>
       </c>
-      <c r="R10" s="38">
+      <c r="R10" s="33">
         <v>1.2584206034913306</v>
       </c>
-      <c r="S10" s="41">
+      <c r="S10" s="32">
         <v>2.2312343573160249</v>
       </c>
-      <c r="T10" s="41">
+      <c r="T10" s="32">
         <v>1.2089851778417198</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="U10" s="37">
+        <v>0.51960082779834738</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="7">
         <v>4.6565114226249769</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="7">
         <v>4.6046322600536138</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="7">
         <v>5.7195375458056068</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="7">
         <v>4.0824499365276239</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="7">
         <v>4.7889325852382116</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="7">
         <v>7.8986267673177402</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="7">
         <v>6.6</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="7">
         <v>3.3</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="7">
         <v>3.5</v>
       </c>
-      <c r="M11" s="10">
+      <c r="M11" s="7">
         <v>2.4</v>
       </c>
-      <c r="N11" s="11">
+      <c r="N11" s="8">
         <v>2.7</v>
       </c>
-      <c r="O11" s="22">
+      <c r="O11" s="19">
         <v>1.6733573069656844</v>
       </c>
-      <c r="P11" s="38">
+      <c r="P11" s="33">
         <v>2.2974019665760834</v>
       </c>
-      <c r="Q11" s="38">
+      <c r="Q11" s="33">
         <v>0.63595936855594293</v>
       </c>
-      <c r="R11" s="38">
+      <c r="R11" s="33">
         <v>0.79202525610136665</v>
       </c>
-      <c r="S11" s="38">
+      <c r="S11" s="33">
         <v>2.4764236727529938</v>
       </c>
-      <c r="T11" s="38">
+      <c r="T11" s="33">
         <v>1.521116134174612</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="U11" s="38">
+        <v>0.59810401028738902</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="7">
         <v>7.0837010111477223</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="7">
         <v>8.2004592257166404</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="7">
         <v>6.8908896532307446</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="7">
         <v>7.7595923110199791</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="7">
         <v>4.7764798489868134</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="7">
         <v>9.9302633206051087</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="7">
         <v>7.7</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K12" s="7">
         <v>8.3000000000000007</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12" s="7">
         <v>5.3</v>
       </c>
-      <c r="M12" s="10">
+      <c r="M12" s="7">
         <v>2.8</v>
       </c>
-      <c r="N12" s="11">
+      <c r="N12" s="8">
         <v>3.9</v>
       </c>
-      <c r="O12" s="22">
+      <c r="O12" s="19">
         <v>3.6369347252874413</v>
       </c>
-      <c r="P12" s="38">
+      <c r="P12" s="33">
         <v>4.0504983733198534</v>
       </c>
-      <c r="Q12" s="38">
+      <c r="Q12" s="33">
         <v>1.2888424905592288</v>
       </c>
-      <c r="R12" s="38">
+      <c r="R12" s="33">
         <v>1.7183687369364922</v>
       </c>
-      <c r="S12" s="38">
+      <c r="S12" s="33">
         <v>1.9888745417939038</v>
       </c>
-      <c r="T12" s="38">
+      <c r="T12" s="33">
         <v>0.9008846687447073</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="34" t="s">
+      <c r="U12" s="38">
+        <v>0.4422117663706796</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="7">
         <v>10.136497149110177</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="7">
         <v>7.3333776391565699</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="7">
         <v>9.1013963817398693</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="7">
         <v>9.2567297554191388</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="7">
         <v>10.980096893752997</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="7">
         <v>8.2095612544209597</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="7">
         <v>9.9</v>
       </c>
-      <c r="K13" s="10">
+      <c r="K13" s="7">
         <v>6.9</v>
       </c>
-      <c r="L13" s="10">
+      <c r="L13" s="7">
         <v>5.4</v>
       </c>
-      <c r="M13" s="10">
+      <c r="M13" s="7">
         <v>4.4000000000000004</v>
       </c>
-      <c r="N13" s="11">
+      <c r="N13" s="8">
         <v>4.5999999999999996</v>
       </c>
-      <c r="O13" s="22">
+      <c r="O13" s="19">
         <v>6.1680928668062025</v>
       </c>
-      <c r="P13" s="38">
+      <c r="P13" s="33">
         <v>2.2316583047106251</v>
       </c>
-      <c r="Q13" s="38">
+      <c r="Q13" s="33">
         <v>1.6032353288937073</v>
       </c>
-      <c r="R13" s="38">
+      <c r="R13" s="33">
         <v>1.7860084101151579</v>
       </c>
-      <c r="S13" s="41">
+      <c r="S13" s="32">
         <v>1.3057776932131271</v>
       </c>
-      <c r="T13" s="41">
+      <c r="T13" s="32">
         <v>3.694303753043183</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="U13" s="37">
+        <v>1.0967257253469767</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="7">
         <v>6.8137219274656591</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="7">
         <v>5.881022393123728</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="7">
         <v>5.8484267731980095</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="7">
         <v>4.9176736721163428</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="7">
         <v>7.995522507395858</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="7">
         <v>7.0428114903469465</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="7">
         <v>6.5</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="7">
         <v>5.2</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="7">
         <v>4.7</v>
       </c>
-      <c r="M14" s="10">
+      <c r="M14" s="7">
         <v>2.5</v>
       </c>
-      <c r="N14" s="11">
+      <c r="N14" s="8">
         <v>5.4</v>
       </c>
-      <c r="O14" s="22">
+      <c r="O14" s="19">
         <v>2.8660803485153701</v>
       </c>
-      <c r="P14" s="38">
+      <c r="P14" s="33">
         <v>2.0206837185430064</v>
       </c>
-      <c r="Q14" s="38">
+      <c r="Q14" s="33">
         <v>2.4146715443031859</v>
       </c>
-      <c r="R14" s="38">
+      <c r="R14" s="33">
         <v>1.5807090270340762</v>
       </c>
-      <c r="S14" s="38">
+      <c r="S14" s="33">
         <v>2.6056788910230639</v>
       </c>
-      <c r="T14" s="38">
+      <c r="T14" s="33">
         <v>4.0607488020791038</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="U14" s="38">
+        <v>1.0973896757579304</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="7">
         <v>13.555772655669351</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="7">
         <v>8.8244446405432146</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="7">
         <v>12.430309698864239</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="7">
         <v>13.683759202328064</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="7">
         <v>14.018522538166559</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="7">
         <v>9.3954686996671324</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="7">
         <v>13.3</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15" s="7">
         <v>8.6999999999999993</v>
       </c>
-      <c r="L15" s="10">
+      <c r="L15" s="7">
         <v>6</v>
       </c>
-      <c r="M15" s="10">
+      <c r="M15" s="7">
         <v>6.4</v>
       </c>
-      <c r="N15" s="11">
+      <c r="N15" s="8">
         <v>3.8</v>
       </c>
-      <c r="O15" s="22">
+      <c r="O15" s="19">
         <v>9.4987156084546829</v>
       </c>
-      <c r="P15" s="38">
+      <c r="P15" s="33">
         <v>2.4443303756935784</v>
       </c>
-      <c r="Q15" s="38">
+      <c r="Q15" s="33">
         <v>0.79837132250209564</v>
       </c>
-      <c r="R15" s="38">
+      <c r="R15" s="33">
         <v>1.9930959157478496</v>
       </c>
-      <c r="S15" s="38">
+      <c r="S15" s="33">
         <v>0</v>
       </c>
-      <c r="T15" s="38">
+      <c r="T15" s="33">
         <v>3.327319511401615</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="32" t="s">
+      <c r="U15" s="38">
+        <v>1.0960625778661124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="7">
         <v>12.055783275906322</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="7">
         <v>7.0007039596759446</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="7">
         <v>11.614177038771993</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="7">
         <v>7.6699762614234706</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="7">
         <v>11.003938651144789</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="7">
         <v>6.7536385227541338</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J16" s="7">
         <v>6.7</v>
       </c>
-      <c r="K16" s="10">
+      <c r="K16" s="7">
         <v>4.4000000000000004</v>
       </c>
-      <c r="L16" s="10">
+      <c r="L16" s="7">
         <v>2.2000000000000002</v>
       </c>
-      <c r="M16" s="10">
+      <c r="M16" s="7">
         <v>4.3</v>
       </c>
-      <c r="N16" s="11">
+      <c r="N16" s="8">
         <v>2.8</v>
       </c>
-      <c r="O16" s="22">
+      <c r="O16" s="19">
         <v>3.1527728637336541</v>
       </c>
-      <c r="P16" s="38">
+      <c r="P16" s="33">
         <v>1.7340940225779042</v>
       </c>
-      <c r="Q16" s="38">
+      <c r="Q16" s="33">
         <v>1.3751327862596732</v>
       </c>
-      <c r="R16" s="38">
+      <c r="R16" s="33">
         <v>1.0231016349164126</v>
       </c>
-      <c r="S16" s="41">
+      <c r="S16" s="32">
         <v>0.65058422463372112</v>
       </c>
-      <c r="T16" s="41">
+      <c r="T16" s="32">
         <v>0.32236434908190637</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="U16" s="37">
+        <v>1.2760066097142384</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="7">
         <v>10.989959886646414</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="7">
         <v>7.0714689798227424</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="7">
         <v>3.9166842917459794</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="7">
         <v>4.6612802983219392</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="7">
         <v>9.2313373130654188</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="7">
         <v>5.3305309970377479</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="7">
         <v>4.5</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="7">
         <v>2.2000000000000002</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L17" s="7">
         <v>1.5</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M17" s="7">
         <v>1.5</v>
       </c>
-      <c r="N17" s="11">
+      <c r="N17" s="8">
         <v>3.6</v>
       </c>
-      <c r="O17" s="22">
+      <c r="O17" s="19">
         <v>2.8530670470756063</v>
       </c>
-      <c r="P17" s="38">
+      <c r="P17" s="33">
         <v>1.4128185022711057</v>
       </c>
-      <c r="Q17" s="38">
+      <c r="Q17" s="33">
         <v>0.67516929870164943</v>
       </c>
-      <c r="R17" s="38">
+      <c r="R17" s="33">
         <v>0</v>
       </c>
-      <c r="S17" s="38">
+      <c r="S17" s="33">
         <v>0.65686622262510019</v>
       </c>
-      <c r="T17" s="38">
+      <c r="T17" s="33">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="U17" s="38">
+        <v>1.9404413857338749</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="7">
         <v>13.102220441005326</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="7">
         <v>6.93134121452501</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="7">
         <v>19.135679622797483</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="7">
         <v>10.603088528215576</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="7">
         <v>12.72931486334706</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="7">
         <v>8.1358539688174911</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="7">
         <v>8.8000000000000007</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="7">
         <v>6.5</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="7">
         <v>2.9</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="7">
         <v>7.1</v>
       </c>
-      <c r="N18" s="11">
+      <c r="N18" s="8">
         <v>2.1</v>
       </c>
-      <c r="O18" s="22">
+      <c r="O18" s="19">
         <v>3.4420327268471667</v>
       </c>
-      <c r="P18" s="38">
+      <c r="P18" s="33">
         <v>2.0439587392862495</v>
       </c>
-      <c r="Q18" s="38">
+      <c r="Q18" s="33">
         <v>2.1012817818869509</v>
       </c>
-      <c r="R18" s="38">
+      <c r="R18" s="33">
         <v>2.0091214112068791</v>
       </c>
-      <c r="S18" s="38">
+      <c r="S18" s="33">
         <v>0.64442124527961442</v>
       </c>
-      <c r="T18" s="38">
+      <c r="T18" s="33">
         <v>0.63756806039044667</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
+      <c r="U18" s="38">
+        <v>0.62942961088661453</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="7">
         <v>3.7970451579802309</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="7">
         <v>4.1173273604637757</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="7">
         <v>7.4807595764988779</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="7">
         <v>8.3602447239296005</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="7">
         <v>6.4073363123058593</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="7">
         <v>4.2223870963850336</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="7">
         <v>5.0999999999999996</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="7">
         <v>6.3</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="7">
         <v>3.5</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M19" s="7">
         <v>4.5999999999999996</v>
       </c>
-      <c r="N19" s="11">
+      <c r="N19" s="8">
         <v>5.9</v>
       </c>
-      <c r="O19" s="22">
+      <c r="O19" s="19">
         <v>4.4429550922666223</v>
       </c>
-      <c r="P19" s="38">
+      <c r="P19" s="33">
         <v>3.7639543070707724</v>
       </c>
-      <c r="Q19" s="38">
+      <c r="Q19" s="33">
         <v>1.5943738893736428</v>
       </c>
-      <c r="R19" s="38">
+      <c r="R19" s="33">
         <v>2.2092990108041848</v>
       </c>
-      <c r="S19" s="41">
+      <c r="S19" s="32">
         <v>2.5553368555544047</v>
       </c>
-      <c r="T19" s="41">
+      <c r="T19" s="32">
         <v>2.1691385808410835</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="U19" s="37">
+        <v>1.2098128632996863</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="7">
         <v>3.9205948849305403</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="7">
         <v>3.5045069804245617</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="7">
         <v>5.2698240787348061</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="7">
         <v>6.4516822761535071</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="7">
         <v>5.833243477815115</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="7">
         <v>3.2982618160229555</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="7">
         <v>4.5999999999999996</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="7">
         <v>5</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="7">
         <v>2.6</v>
       </c>
-      <c r="M20" s="10">
+      <c r="M20" s="7">
         <v>2.4</v>
       </c>
-      <c r="N20" s="11">
+      <c r="N20" s="8">
         <v>5.3</v>
       </c>
-      <c r="O20" s="22">
+      <c r="O20" s="19">
         <v>3.0438620521717956</v>
       </c>
-      <c r="P20" s="38">
+      <c r="P20" s="33">
         <v>2.2387992871663069</v>
       </c>
-      <c r="Q20" s="38">
+      <c r="Q20" s="33">
         <v>1.5765365498500856</v>
       </c>
-      <c r="R20" s="38">
+      <c r="R20" s="33">
         <v>0.86496336159360854</v>
       </c>
-      <c r="S20" s="38">
+      <c r="S20" s="33">
         <v>1.807815324711445</v>
       </c>
-      <c r="T20" s="38">
+      <c r="T20" s="33">
         <v>1.5024572004578396</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="U20" s="38">
+        <v>1.0069276623167391</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="7">
         <v>3.6754301172094661</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="7">
         <v>4.7205523772520213</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="7">
         <v>9.6564796766867556</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="7">
         <v>10.240564996689473</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="7">
         <v>6.9735493274011677</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="7">
         <v>5.1332945484411896</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="7">
         <v>5.5</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K21" s="7">
         <v>7.7</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="7">
         <v>4.5</v>
       </c>
-      <c r="M21" s="10">
+      <c r="M21" s="7">
         <v>6.8</v>
       </c>
-      <c r="N21" s="11">
+      <c r="N21" s="8">
         <v>6.5</v>
       </c>
-      <c r="O21" s="22">
+      <c r="O21" s="19">
         <v>5.8132168702534717</v>
       </c>
-      <c r="P21" s="38">
+      <c r="P21" s="33">
         <v>5.2558120521610148</v>
       </c>
-      <c r="Q21" s="38">
+      <c r="Q21" s="33">
         <v>1.6126194804433236</v>
       </c>
-      <c r="R21" s="38">
+      <c r="R21" s="33">
         <v>3.5236628052020538</v>
       </c>
-      <c r="S21" s="38">
+      <c r="S21" s="33">
         <v>3.2928586128833093</v>
       </c>
-      <c r="T21" s="38">
+      <c r="T21" s="33">
         <v>2.8259763748375066</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="32" t="s">
+      <c r="U21" s="38">
+        <v>1.4084665742712592</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="7">
         <v>7.6350277106593962</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="7">
         <v>5.7766994605451423</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="7">
         <v>4.8320001405672768</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="7">
         <v>11.284379380834784</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="7">
         <v>8.1345018473881829</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="7">
         <v>8.4240320787141556</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="7">
         <v>7.9</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="7">
         <v>6.5</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22" s="7">
         <v>5.2</v>
       </c>
-      <c r="M22" s="10">
+      <c r="M22" s="7">
         <v>6.3</v>
       </c>
-      <c r="N22" s="11">
+      <c r="N22" s="8">
         <v>3.9</v>
       </c>
-      <c r="O22" s="22">
+      <c r="O22" s="19">
         <v>2.6798771850570047</v>
       </c>
-      <c r="P22" s="38">
+      <c r="P22" s="33">
         <v>1.8839771511251113</v>
       </c>
-      <c r="Q22" s="38">
+      <c r="Q22" s="33">
         <v>0.37150276583809166</v>
       </c>
-      <c r="R22" s="38">
+      <c r="R22" s="33">
         <v>1.4678252700798498</v>
       </c>
-      <c r="S22" s="41">
+      <c r="S22" s="32">
         <v>1.8387963974300983</v>
       </c>
-      <c r="T22" s="41">
+      <c r="T22" s="32">
         <v>6.1744985943935555</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="U22" s="37">
+        <v>1.0760247342218907</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="7">
         <v>10.776345920704054</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="7">
         <v>7.1138301750891451</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="7">
         <v>3.5200422405068856</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="7">
         <v>13.057330385278295</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="7">
         <v>6.0208838657514923</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23" s="7">
         <v>6.7797184721904431</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="7">
         <v>5</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23" s="7">
         <v>5.8</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L23" s="7">
         <v>2.4</v>
       </c>
-      <c r="M23" s="10">
+      <c r="M23" s="7">
         <v>5.6</v>
       </c>
-      <c r="N23" s="11">
+      <c r="N23" s="8">
         <v>1.6</v>
       </c>
-      <c r="O23" s="22">
+      <c r="O23" s="19">
         <v>3.0962628107873797</v>
       </c>
-      <c r="P23" s="38">
+      <c r="P23" s="33">
         <v>1.5242392141022612</v>
       </c>
-      <c r="Q23" s="38">
+      <c r="Q23" s="33">
         <v>0</v>
       </c>
-      <c r="R23" s="38">
+      <c r="R23" s="33">
         <v>0.74155920237892192</v>
       </c>
-      <c r="S23" s="38">
+      <c r="S23" s="33">
         <v>2.2260807622100529</v>
       </c>
-      <c r="T23" s="38">
+      <c r="T23" s="33">
         <v>4.3993752887090034</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="U23" s="38">
+        <v>0.72519997389280089</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="7">
         <v>4.4922418982417369</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="7">
         <v>4.4410889550117689</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="7">
         <v>6.139596891609802</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="7">
         <v>9.5214188645275204</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="7">
         <v>10.229219766262327</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="7">
         <v>10.0488205196915</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="7">
         <v>10.7</v>
       </c>
-      <c r="K24" s="10">
+      <c r="K24" s="7">
         <v>7.3</v>
       </c>
-      <c r="L24" s="10">
+      <c r="L24" s="7">
         <v>8</v>
       </c>
-      <c r="M24" s="10">
+      <c r="M24" s="7">
         <v>7</v>
       </c>
-      <c r="N24" s="11">
+      <c r="N24" s="8">
         <v>6.2</v>
       </c>
-      <c r="O24" s="22">
+      <c r="O24" s="19">
         <v>2.2724173976275961</v>
       </c>
-      <c r="P24" s="38">
+      <c r="P24" s="33">
         <v>2.2357526661350544</v>
       </c>
-      <c r="Q24" s="38">
+      <c r="Q24" s="33">
         <v>0.75125835774923</v>
       </c>
-      <c r="R24" s="38">
+      <c r="R24" s="33">
         <v>2.1792664589099311</v>
       </c>
-      <c r="S24" s="38">
+      <c r="S24" s="33">
         <v>1.4582467499325562</v>
       </c>
-      <c r="T24" s="38">
+      <c r="T24" s="33">
         <v>7.9169155696940479</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="32" t="s">
+      <c r="U24" s="38">
+        <v>1.4193356090014264</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="33" t="s">
+      <c r="C25" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="7">
         <v>12.255614208426303</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="7">
         <v>13.153625577663389</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="7">
         <v>11.182041144941618</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="7">
         <v>6.530648456425789</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="7">
         <v>10.259855262756115</v>
       </c>
-      <c r="I25" s="10">
+      <c r="I25" s="7">
         <v>8.790298400526936</v>
       </c>
-      <c r="J25" s="10">
+      <c r="J25" s="7">
         <v>6.6</v>
       </c>
-      <c r="K25" s="10">
+      <c r="K25" s="7">
         <v>6.5</v>
       </c>
-      <c r="L25" s="10">
+      <c r="L25" s="7">
         <v>5.8</v>
       </c>
-      <c r="M25" s="10">
+      <c r="M25" s="7">
         <v>5.4</v>
       </c>
-      <c r="N25" s="11">
+      <c r="N25" s="8">
         <v>4.8</v>
       </c>
-      <c r="O25" s="22">
+      <c r="O25" s="19">
         <v>6.3343461129660845</v>
       </c>
-      <c r="P25" s="38">
+      <c r="P25" s="33">
         <v>5.0499258818170052</v>
       </c>
-      <c r="Q25" s="38">
+      <c r="Q25" s="33">
         <v>2.8942542850468351</v>
       </c>
-      <c r="R25" s="38">
+      <c r="R25" s="33">
         <v>1.5302890103825006</v>
       </c>
-      <c r="S25" s="41">
+      <c r="S25" s="32">
         <v>1.2245886088767601</v>
       </c>
-      <c r="T25" s="41">
+      <c r="T25" s="32">
         <v>2.8763040791558883</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="U25" s="37">
+        <v>1.866410622779749</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="7">
         <v>9.1810730937486831</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="7">
         <v>8.6121835330129599</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="7">
         <v>7.0802164104767673</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="7">
         <v>6.0564362959804647</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="7">
         <v>8.8910035059389507</v>
       </c>
-      <c r="I26" s="10">
+      <c r="I26" s="7">
         <v>7.1120045896136279</v>
       </c>
-      <c r="J26" s="10">
+      <c r="J26" s="7">
         <v>6.3</v>
       </c>
-      <c r="K26" s="10">
+      <c r="K26" s="7">
         <v>3.9</v>
       </c>
-      <c r="L26" s="10">
+      <c r="L26" s="7">
         <v>4.7</v>
       </c>
-      <c r="M26" s="10">
+      <c r="M26" s="7">
         <v>4.2</v>
       </c>
-      <c r="N26" s="11">
+      <c r="N26" s="8">
         <v>2.6</v>
       </c>
-      <c r="O26" s="22">
+      <c r="O26" s="19">
         <v>4.8647185231560606</v>
       </c>
-      <c r="P26" s="38">
+      <c r="P26" s="33">
         <v>3.7317455447104577</v>
       </c>
-      <c r="Q26" s="38">
+      <c r="Q26" s="33">
         <v>2.72898263527357</v>
       </c>
-      <c r="R26" s="38">
+      <c r="R26" s="33">
         <v>0.80351618683358383</v>
       </c>
-      <c r="S26" s="38">
+      <c r="S26" s="33">
         <v>1.3105423773238725</v>
       </c>
-      <c r="T26" s="38">
+      <c r="T26" s="33">
         <v>1.4751329463567904</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+      <c r="U26" s="38">
+        <v>1.4505727690190813</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="7">
         <v>15.445168365206154</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="7">
         <v>17.863613860122801</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="7">
         <v>15.43248918460799</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="7">
         <v>7.0215209617477568</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="7">
         <v>11.67487219740967</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27" s="7">
         <v>10.522735225957385</v>
       </c>
-      <c r="J27" s="10">
+      <c r="J27" s="7">
         <v>7</v>
       </c>
-      <c r="K27" s="10">
+      <c r="K27" s="7">
         <v>9.1999999999999993</v>
       </c>
-      <c r="L27" s="10">
+      <c r="L27" s="7">
         <v>6.9</v>
       </c>
-      <c r="M27" s="10">
+      <c r="M27" s="7">
         <v>6.6</v>
       </c>
-      <c r="N27" s="11">
+      <c r="N27" s="8">
         <v>7.1</v>
       </c>
-      <c r="O27" s="22">
+      <c r="O27" s="19">
         <v>7.8493277922893432</v>
       </c>
-      <c r="P27" s="38">
+      <c r="P27" s="33">
         <v>6.4080519308528485</v>
       </c>
-      <c r="Q27" s="38">
+      <c r="Q27" s="33">
         <v>3.0545792215303034</v>
       </c>
-      <c r="R27" s="38">
+      <c r="R27" s="33">
         <v>2.280288974802807</v>
       </c>
-      <c r="S27" s="38">
+      <c r="S27" s="33">
         <v>1.1375464261135158</v>
       </c>
-      <c r="T27" s="38">
+      <c r="T27" s="33">
         <v>4.2954684675262591</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="32" t="s">
+      <c r="U27" s="38">
+        <v>2.2828681124831376</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="30" t="s">
+      <c r="B28" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="7">
         <v>19.444498796642339</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="7">
         <v>16.559633415648008</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="7">
         <v>18.582511712342718</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="7">
         <v>17.465078633879205</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="7">
         <v>16.6075407461399</v>
       </c>
-      <c r="I28" s="10">
+      <c r="I28" s="7">
         <v>17.864088207892763</v>
       </c>
-      <c r="J28" s="10">
+      <c r="J28" s="7">
         <v>10.1</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K28" s="7">
         <v>9.5</v>
       </c>
-      <c r="L28" s="10">
+      <c r="L28" s="7">
         <v>7.9</v>
       </c>
-      <c r="M28" s="10">
+      <c r="M28" s="7">
         <v>10.1</v>
       </c>
-      <c r="N28" s="11">
+      <c r="N28" s="8">
         <v>10.1</v>
       </c>
-      <c r="O28" s="22">
+      <c r="O28" s="19">
         <v>8.9682121228546521</v>
       </c>
-      <c r="P28" s="38">
+      <c r="P28" s="33">
         <v>5.1894135962636225</v>
       </c>
-      <c r="Q28" s="38">
+      <c r="Q28" s="33">
         <v>3.9473869708034344</v>
       </c>
-      <c r="R28" s="38">
+      <c r="R28" s="33">
         <v>2.3014726663297309</v>
       </c>
-      <c r="S28" s="41">
+      <c r="S28" s="32">
         <v>2.4791112740241377</v>
       </c>
-      <c r="T28" s="41">
+      <c r="T28" s="32">
         <v>1.8177568880002077</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="U28" s="37">
+        <v>2.2929977199959337</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="7">
         <v>15.31036626052302</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="7">
         <v>11.046410705550032</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="7">
         <v>10.882673673035622</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="7">
         <v>9.8426703820924644</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="7">
         <v>10.767229720999543</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I29" s="7">
         <v>7.8177657670601608</v>
       </c>
-      <c r="J29" s="10">
+      <c r="J29" s="7">
         <v>7.4</v>
       </c>
-      <c r="K29" s="10">
+      <c r="K29" s="7">
         <v>7.1</v>
       </c>
-      <c r="L29" s="10">
+      <c r="L29" s="7">
         <v>4.5999999999999996</v>
       </c>
-      <c r="M29" s="10">
+      <c r="M29" s="7">
         <v>7</v>
       </c>
-      <c r="N29" s="11">
+      <c r="N29" s="8">
         <v>7.6</v>
       </c>
-      <c r="O29" s="22">
+      <c r="O29" s="19">
         <v>5.9295385521919837</v>
       </c>
-      <c r="P29" s="38">
+      <c r="P29" s="33">
         <v>2.8949477733328264</v>
       </c>
-      <c r="Q29" s="38">
+      <c r="Q29" s="33">
         <v>3.6031203021816895</v>
       </c>
-      <c r="R29" s="38">
+      <c r="R29" s="33">
         <v>1.7358308467556451</v>
       </c>
-      <c r="S29" s="38">
+      <c r="S29" s="33">
         <v>2.4279584268771761</v>
       </c>
-      <c r="T29" s="38">
+      <c r="T29" s="33">
         <v>1.581380197008345</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+      <c r="U29" s="38">
+        <v>1.1204356253711443</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="7">
         <v>24.204156800841883</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="7">
         <v>22.932791285539313</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="7">
         <v>27.489325406816327</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="7">
         <v>26.266738731821647</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="7">
         <v>23.342206682824109</v>
       </c>
-      <c r="I30" s="10">
+      <c r="I30" s="7">
         <v>29.427859184045722</v>
       </c>
-      <c r="J30" s="10">
+      <c r="J30" s="7">
         <v>13.1</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="7">
         <v>12.3</v>
       </c>
-      <c r="L30" s="10">
+      <c r="L30" s="7">
         <v>11.8</v>
       </c>
-      <c r="M30" s="10">
+      <c r="M30" s="7">
         <v>13.7</v>
       </c>
-      <c r="N30" s="11">
+      <c r="N30" s="8">
         <v>12.9</v>
       </c>
-      <c r="O30" s="22">
+      <c r="O30" s="19">
         <v>12.420425073259457</v>
       </c>
-      <c r="P30" s="38">
+      <c r="P30" s="33">
         <v>7.7885929906762339</v>
       </c>
-      <c r="Q30" s="38">
+      <c r="Q30" s="33">
         <v>4.2520923837938582</v>
       </c>
-      <c r="R30" s="38">
+      <c r="R30" s="33">
         <v>2.9402079315049163</v>
       </c>
-      <c r="S30" s="38">
+      <c r="S30" s="33">
         <v>2.5408788313520994</v>
       </c>
-      <c r="T30" s="38">
+      <c r="T30" s="33">
         <v>2.103608453446189</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="32" t="s">
+      <c r="U30" s="38">
+        <v>3.7016908314165864</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="30" t="s">
+      <c r="B31" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="30" t="s">
+      <c r="C31" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="7">
         <v>40.964579293770655</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="7">
         <v>24.854561977180406</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="7">
         <v>23.592385460902388</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="7">
         <v>13.593447181690015</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="7">
         <v>19.15207135514585</v>
       </c>
-      <c r="I31" s="10">
+      <c r="I31" s="7">
         <v>29.440247917877205</v>
       </c>
-      <c r="J31" s="11">
+      <c r="J31" s="8">
         <v>21.3</v>
       </c>
-      <c r="K31" s="11">
+      <c r="K31" s="8">
         <v>24.7</v>
       </c>
-      <c r="L31" s="11">
+      <c r="L31" s="8">
         <v>22.3</v>
       </c>
-      <c r="M31" s="22">
+      <c r="M31" s="19">
         <v>14</v>
       </c>
-      <c r="N31" s="11">
+      <c r="N31" s="8">
         <v>4.9000000000000004</v>
       </c>
-      <c r="O31" s="22">
+      <c r="O31" s="19">
         <v>7.4795078483835766</v>
       </c>
-      <c r="P31" s="38">
+      <c r="P31" s="33">
         <v>4.5752680616876855</v>
       </c>
-      <c r="Q31" s="38">
+      <c r="Q31" s="33">
         <v>0</v>
       </c>
-      <c r="R31" s="38">
+      <c r="R31" s="33">
         <v>1.2198989923634325</v>
       </c>
-      <c r="S31" s="41">
+      <c r="S31" s="32">
         <v>1.1238322680339958</v>
       </c>
-      <c r="T31" s="41">
+      <c r="T31" s="32">
         <v>1.3736037318066185</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="20" t="s">
+      <c r="U31" s="37">
+        <v>1.2810849935838993</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="7">
         <v>35.243744235398218</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="7">
         <v>19.402116323149709</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="7">
         <v>14.139324437961854</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="7">
         <v>11.947431302270012</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="7">
         <v>11.255261834907818</v>
       </c>
-      <c r="I32" s="8">
+      <c r="I32" s="5">
         <v>20.837209302325579</v>
       </c>
-      <c r="J32" s="19">
+      <c r="J32" s="16">
         <v>12.4</v>
       </c>
-      <c r="K32" s="19">
+      <c r="K32" s="16">
         <v>20.9</v>
       </c>
-      <c r="L32" s="19">
+      <c r="L32" s="16">
         <v>14.9</v>
       </c>
-      <c r="M32" s="19">
+      <c r="M32" s="16">
         <v>12.5</v>
       </c>
-      <c r="N32" s="19">
+      <c r="N32" s="16">
         <v>4.0999999999999996</v>
       </c>
-      <c r="O32" s="22">
+      <c r="O32" s="19">
         <v>3.953532811027721</v>
       </c>
-      <c r="P32" s="39">
+      <c r="P32" s="33">
         <v>2.5372017202227664</v>
       </c>
-      <c r="Q32" s="39">
+      <c r="Q32" s="33">
         <v>0</v>
       </c>
-      <c r="R32" s="39">
+      <c r="R32" s="33">
         <v>1.1878318505232399</v>
       </c>
-      <c r="S32" s="39">
+      <c r="S32" s="33">
         <v>0.57553956834532372</v>
       </c>
-      <c r="T32" s="39">
+      <c r="T32" s="33">
         <v>2.249820014398848</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="21" t="s">
+      <c r="U32" s="38">
+        <v>0.86466295438038243</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="9">
         <v>47.169044094923635</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="9">
         <v>30.771224046901825</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="9">
         <v>33.821599117417314</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="9">
         <v>15.377518068583731</v>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="9">
         <v>27.737893225427491</v>
       </c>
-      <c r="I33" s="25">
+      <c r="I33" s="22">
         <v>38.78004443546758</v>
       </c>
-      <c r="J33" s="13">
+      <c r="J33" s="10">
         <v>30.9</v>
       </c>
-      <c r="K33" s="13">
+      <c r="K33" s="10">
         <v>28.7</v>
       </c>
-      <c r="L33" s="13">
+      <c r="L33" s="10">
         <v>30.4</v>
       </c>
-      <c r="M33" s="13">
+      <c r="M33" s="10">
         <v>15.6</v>
       </c>
-      <c r="N33" s="13">
+      <c r="N33" s="10">
         <v>5.8</v>
       </c>
-      <c r="O33" s="24">
+      <c r="O33" s="21">
         <v>11.238006939469285</v>
       </c>
-      <c r="P33" s="40">
+      <c r="P33" s="34">
         <v>6.7413155003067295</v>
       </c>
-      <c r="Q33" s="40">
+      <c r="Q33" s="34">
         <v>0</v>
       </c>
-      <c r="R33" s="40">
+      <c r="R33" s="34">
         <v>1.2537455648750642</v>
       </c>
-      <c r="S33" s="40">
+      <c r="S33" s="34">
         <v>1.6467682173734046</v>
       </c>
-      <c r="T33" s="40">
+      <c r="T33" s="34">
         <v>0.53701655085009725</v>
+      </c>
+      <c r="U33" s="39">
+        <v>1.6874148382823804</v>
       </c>
     </row>
   </sheetData>
